--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,6 +1378,1623 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122291593</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>404072</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7064465</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122291590</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>403811</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7064538</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122291598</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>403536</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7064668</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122291599</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>403740</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7064407</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122291613</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78643</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>403571</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7064657</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122291614</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78643</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>403721</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7064419</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122291597</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>403599</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7064658</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122291595</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>403755</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7064690</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122291594</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>404077</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7064478</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122291596</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>403524</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7065024</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122291592</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>403956</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7064405</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122291611</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57319</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>102620</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Surnia ulula</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>403666</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7064579</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122291591</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>403825</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7064511</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122291589</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>403803</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7064528</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122291588</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nötnäsdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>403772</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7064456</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291593</v>
+        <v>122291611</v>
       </c>
       <c r="B8" t="n">
-        <v>57372</v>
+        <v>57321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,20 +1393,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102620</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1414,17 +1414,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404072</v>
+        <v>403666</v>
       </c>
       <c r="R8" t="n">
-        <v>7064465</v>
+        <v>7064579</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1473,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1500,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291590</v>
+        <v>122291594</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,10 +1540,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403811</v>
+        <v>404077</v>
       </c>
       <c r="R9" t="n">
-        <v>7064538</v>
+        <v>7064478</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1580,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291598</v>
+        <v>122291597</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403536</v>
+        <v>403599</v>
       </c>
       <c r="R10" t="n">
-        <v>7064668</v>
+        <v>7064658</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1687,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1714,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291599</v>
+        <v>122291596</v>
       </c>
       <c r="B11" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403740</v>
+        <v>403524</v>
       </c>
       <c r="R11" t="n">
-        <v>7064407</v>
+        <v>7065024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1794,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291613</v>
+        <v>122291592</v>
       </c>
       <c r="B12" t="n">
-        <v>78643</v>
+        <v>57374</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,21 +1837,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1849,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403571</v>
+        <v>403956</v>
       </c>
       <c r="R12" t="n">
-        <v>7064657</v>
+        <v>7064405</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1901,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291614</v>
+        <v>122291598</v>
       </c>
       <c r="B13" t="n">
-        <v>78643</v>
+        <v>57374</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,21 +1944,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1968,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403721</v>
+        <v>403536</v>
       </c>
       <c r="R13" t="n">
-        <v>7064419</v>
+        <v>7064668</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,7 +2008,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291597</v>
+        <v>122291590</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,10 +2075,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403599</v>
+        <v>403811</v>
       </c>
       <c r="R14" t="n">
-        <v>7064658</v>
+        <v>7064538</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291595</v>
+        <v>122291613</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>78645</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,21 +2158,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403755</v>
+        <v>403571</v>
       </c>
       <c r="R15" t="n">
-        <v>7064690</v>
+        <v>7064657</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2222,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291594</v>
+        <v>122291589</v>
       </c>
       <c r="B16" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404077</v>
+        <v>403803</v>
       </c>
       <c r="R16" t="n">
-        <v>7064478</v>
+        <v>7064528</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2329,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,10 +2356,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291596</v>
+        <v>122291593</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403524</v>
+        <v>404072</v>
       </c>
       <c r="R17" t="n">
-        <v>7065024</v>
+        <v>7064465</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2424,7 +2436,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291592</v>
+        <v>122291614</v>
       </c>
       <c r="B18" t="n">
-        <v>57372</v>
+        <v>78645</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2491,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403956</v>
+        <v>403721</v>
       </c>
       <c r="R18" t="n">
-        <v>7064405</v>
+        <v>7064419</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,7 +2543,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,10 +2570,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291611</v>
+        <v>122291595</v>
       </c>
       <c r="B19" t="n">
-        <v>57319</v>
+        <v>57374</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,20 +2582,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102620</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2591,29 +2603,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403666</v>
+        <v>403755</v>
       </c>
       <c r="R19" t="n">
-        <v>7064579</v>
+        <v>7064690</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,7 +2680,7 @@
         <v>122291591</v>
       </c>
       <c r="B20" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291589</v>
+        <v>122291588</v>
       </c>
       <c r="B21" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403803</v>
+        <v>403772</v>
       </c>
       <c r="R21" t="n">
-        <v>7064528</v>
+        <v>7064456</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2891,10 +2891,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291588</v>
+        <v>122291599</v>
       </c>
       <c r="B22" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>403772</v>
+        <v>403740</v>
       </c>
       <c r="R22" t="n">
-        <v>7064456</v>
+        <v>7064407</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291611</v>
+        <v>122291592</v>
       </c>
       <c r="B8" t="n">
-        <v>57321</v>
+        <v>57374</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,20 +1393,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102620</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1414,29 +1414,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403666</v>
+        <v>403956</v>
       </c>
       <c r="R8" t="n">
-        <v>7064579</v>
+        <v>7064405</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291594</v>
+        <v>122291589</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1540,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404077</v>
+        <v>403803</v>
       </c>
       <c r="R9" t="n">
-        <v>7064478</v>
+        <v>7064528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1568,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291597</v>
+        <v>122291599</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1647,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403599</v>
+        <v>403740</v>
       </c>
       <c r="R10" t="n">
-        <v>7064658</v>
+        <v>7064407</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1675,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291596</v>
+        <v>122291613</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1754,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403524</v>
+        <v>403571</v>
       </c>
       <c r="R11" t="n">
-        <v>7065024</v>
+        <v>7064657</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,7 +1782,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,7 +1809,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291592</v>
+        <v>122291597</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1861,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403956</v>
+        <v>403599</v>
       </c>
       <c r="R12" t="n">
-        <v>7064405</v>
+        <v>7064658</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,7 +1916,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291598</v>
+        <v>122291593</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1968,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403536</v>
+        <v>404072</v>
       </c>
       <c r="R13" t="n">
-        <v>7064668</v>
+        <v>7064465</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,7 +1996,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2142,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291613</v>
+        <v>122291595</v>
       </c>
       <c r="B15" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403571</v>
+        <v>403755</v>
       </c>
       <c r="R15" t="n">
-        <v>7064657</v>
+        <v>7064690</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2210,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291589</v>
+        <v>122291596</v>
       </c>
       <c r="B16" t="n">
         <v>57374</v>
@@ -2289,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403803</v>
+        <v>403524</v>
       </c>
       <c r="R16" t="n">
-        <v>7064528</v>
+        <v>7065024</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2317,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,7 +2344,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291593</v>
+        <v>122291588</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2396,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>404072</v>
+        <v>403772</v>
       </c>
       <c r="R17" t="n">
-        <v>7064465</v>
+        <v>7064456</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2570,7 +2558,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291595</v>
+        <v>122291591</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2610,10 +2598,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403755</v>
+        <v>403825</v>
       </c>
       <c r="R19" t="n">
-        <v>7064690</v>
+        <v>7064511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2677,7 +2665,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291591</v>
+        <v>122291598</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2717,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403825</v>
+        <v>403536</v>
       </c>
       <c r="R20" t="n">
-        <v>7064511</v>
+        <v>7064668</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2757,7 +2745,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2784,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291588</v>
+        <v>122291611</v>
       </c>
       <c r="B21" t="n">
-        <v>57374</v>
+        <v>57321</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2796,20 +2784,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>102620</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2817,17 +2805,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403772</v>
+        <v>403666</v>
       </c>
       <c r="R21" t="n">
-        <v>7064456</v>
+        <v>7064579</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,7 +2891,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291599</v>
+        <v>122291594</v>
       </c>
       <c r="B22" t="n">
         <v>57374</v>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>403740</v>
+        <v>404077</v>
       </c>
       <c r="R22" t="n">
-        <v>7064407</v>
+        <v>7064478</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291592</v>
+        <v>122291594</v>
       </c>
       <c r="B8" t="n">
         <v>57374</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403956</v>
+        <v>404077</v>
       </c>
       <c r="R8" t="n">
-        <v>7064405</v>
+        <v>7064478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291590</v>
+        <v>122291595</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403811</v>
+        <v>403755</v>
       </c>
       <c r="R9" t="n">
-        <v>7064538</v>
+        <v>7064690</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291614</v>
+        <v>122291598</v>
       </c>
       <c r="B10" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403721</v>
+        <v>403536</v>
       </c>
       <c r="R10" t="n">
-        <v>7064419</v>
+        <v>7064668</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291613</v>
+        <v>122291596</v>
       </c>
       <c r="B11" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403571</v>
+        <v>403524</v>
       </c>
       <c r="R11" t="n">
-        <v>7064657</v>
+        <v>7065024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,7 +1809,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291596</v>
+        <v>122291592</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403524</v>
+        <v>403956</v>
       </c>
       <c r="R12" t="n">
-        <v>7065024</v>
+        <v>7064405</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291599</v>
+        <v>122291613</v>
       </c>
       <c r="B13" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403740</v>
+        <v>403571</v>
       </c>
       <c r="R13" t="n">
-        <v>7064407</v>
+        <v>7064657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,7 +2023,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291595</v>
+        <v>122291590</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403755</v>
+        <v>403811</v>
       </c>
       <c r="R14" t="n">
-        <v>7064690</v>
+        <v>7064538</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291591</v>
+        <v>122291589</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403825</v>
+        <v>403803</v>
       </c>
       <c r="R15" t="n">
-        <v>7064511</v>
+        <v>7064528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291597</v>
+        <v>122291599</v>
       </c>
       <c r="B16" t="n">
         <v>57374</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403599</v>
+        <v>403740</v>
       </c>
       <c r="R16" t="n">
-        <v>7064658</v>
+        <v>7064407</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291598</v>
+        <v>122291591</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403536</v>
+        <v>403825</v>
       </c>
       <c r="R18" t="n">
-        <v>7064668</v>
+        <v>7064511</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291594</v>
+        <v>122291611</v>
       </c>
       <c r="B19" t="n">
-        <v>57374</v>
+        <v>57321</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,20 +2570,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>102620</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2591,17 +2591,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>404077</v>
+        <v>403666</v>
       </c>
       <c r="R19" t="n">
-        <v>7064478</v>
+        <v>7064579</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2638,7 +2650,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,10 +2677,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291611</v>
+        <v>122291597</v>
       </c>
       <c r="B20" t="n">
-        <v>57321</v>
+        <v>57374</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2677,20 +2689,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102620</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2698,29 +2710,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403666</v>
+        <v>403599</v>
       </c>
       <c r="R20" t="n">
-        <v>7064579</v>
+        <v>7064658</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2891,10 +2891,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291589</v>
+        <v>122291614</v>
       </c>
       <c r="B22" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2907,21 +2907,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>403803</v>
+        <v>403721</v>
       </c>
       <c r="R22" t="n">
-        <v>7064528</v>
+        <v>7064419</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291594</v>
+        <v>122291596</v>
       </c>
       <c r="B8" t="n">
         <v>57374</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404077</v>
+        <v>403524</v>
       </c>
       <c r="R8" t="n">
-        <v>7064478</v>
+        <v>7065024</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291595</v>
+        <v>122291599</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403755</v>
+        <v>403740</v>
       </c>
       <c r="R9" t="n">
-        <v>7064690</v>
+        <v>7064407</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291598</v>
+        <v>122291613</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403536</v>
+        <v>403571</v>
       </c>
       <c r="R10" t="n">
-        <v>7064668</v>
+        <v>7064657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291596</v>
+        <v>122291588</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403524</v>
+        <v>403772</v>
       </c>
       <c r="R11" t="n">
-        <v>7065024</v>
+        <v>7064456</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,7 +1809,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291592</v>
+        <v>122291589</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403956</v>
+        <v>403803</v>
       </c>
       <c r="R12" t="n">
-        <v>7064405</v>
+        <v>7064528</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291613</v>
+        <v>122291590</v>
       </c>
       <c r="B13" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403571</v>
+        <v>403811</v>
       </c>
       <c r="R13" t="n">
-        <v>7064657</v>
+        <v>7064538</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,7 +2023,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291590</v>
+        <v>122291592</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403811</v>
+        <v>403956</v>
       </c>
       <c r="R14" t="n">
-        <v>7064538</v>
+        <v>7064405</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291589</v>
+        <v>122291591</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403803</v>
+        <v>403825</v>
       </c>
       <c r="R15" t="n">
-        <v>7064528</v>
+        <v>7064511</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291599</v>
+        <v>122291611</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>57321</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>102620</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2270,17 +2270,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403740</v>
+        <v>403666</v>
       </c>
       <c r="R16" t="n">
-        <v>7064407</v>
+        <v>7064579</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2329,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2451,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291591</v>
+        <v>122291614</v>
       </c>
       <c r="B18" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2491,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403825</v>
+        <v>403721</v>
       </c>
       <c r="R18" t="n">
-        <v>7064511</v>
+        <v>7064419</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,7 +2543,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,10 +2570,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291611</v>
+        <v>122291598</v>
       </c>
       <c r="B19" t="n">
-        <v>57321</v>
+        <v>57374</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,20 +2582,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102620</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2591,29 +2603,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403666</v>
+        <v>403536</v>
       </c>
       <c r="R19" t="n">
-        <v>7064579</v>
+        <v>7064668</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2784,7 +2784,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291588</v>
+        <v>122291594</v>
       </c>
       <c r="B21" t="n">
         <v>57374</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403772</v>
+        <v>404077</v>
       </c>
       <c r="R21" t="n">
-        <v>7064456</v>
+        <v>7064478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,10 +2891,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291614</v>
+        <v>122291595</v>
       </c>
       <c r="B22" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2907,21 +2907,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>403721</v>
+        <v>403755</v>
       </c>
       <c r="R22" t="n">
-        <v>7064419</v>
+        <v>7064690</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291596</v>
+        <v>122291594</v>
       </c>
       <c r="B8" t="n">
         <v>57374</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403524</v>
+        <v>404077</v>
       </c>
       <c r="R8" t="n">
-        <v>7065024</v>
+        <v>7064478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291599</v>
+        <v>122291598</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403740</v>
+        <v>403536</v>
       </c>
       <c r="R9" t="n">
-        <v>7064407</v>
+        <v>7064668</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291613</v>
+        <v>122291595</v>
       </c>
       <c r="B10" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403571</v>
+        <v>403755</v>
       </c>
       <c r="R10" t="n">
-        <v>7064657</v>
+        <v>7064690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291588</v>
+        <v>122291597</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403772</v>
+        <v>403599</v>
       </c>
       <c r="R11" t="n">
-        <v>7064456</v>
+        <v>7064658</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1809,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291589</v>
+        <v>122291596</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403803</v>
+        <v>403524</v>
       </c>
       <c r="R12" t="n">
-        <v>7064528</v>
+        <v>7065024</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,7 +1916,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291590</v>
+        <v>122291593</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403811</v>
+        <v>404072</v>
       </c>
       <c r="R13" t="n">
-        <v>7064538</v>
+        <v>7064465</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291592</v>
+        <v>122291611</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>57321</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,20 +2035,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>102620</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2056,17 +2056,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403956</v>
+        <v>403666</v>
       </c>
       <c r="R14" t="n">
-        <v>7064405</v>
+        <v>7064579</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2115,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291591</v>
+        <v>122291613</v>
       </c>
       <c r="B15" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,21 +2158,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403825</v>
+        <v>403571</v>
       </c>
       <c r="R15" t="n">
-        <v>7064511</v>
+        <v>7064657</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2222,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291611</v>
+        <v>122291589</v>
       </c>
       <c r="B16" t="n">
-        <v>57321</v>
+        <v>57374</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,20 +2261,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102620</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2270,29 +2282,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403666</v>
+        <v>403803</v>
       </c>
       <c r="R16" t="n">
-        <v>7064579</v>
+        <v>7064528</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,7 +2356,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291593</v>
+        <v>122291591</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>404072</v>
+        <v>403825</v>
       </c>
       <c r="R17" t="n">
-        <v>7064465</v>
+        <v>7064511</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291614</v>
+        <v>122291590</v>
       </c>
       <c r="B18" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403721</v>
+        <v>403811</v>
       </c>
       <c r="R18" t="n">
-        <v>7064419</v>
+        <v>7064538</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2570,10 +2570,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291598</v>
+        <v>122291614</v>
       </c>
       <c r="B19" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,21 +2586,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403536</v>
+        <v>403721</v>
       </c>
       <c r="R19" t="n">
-        <v>7064668</v>
+        <v>7064419</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,7 +2677,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291597</v>
+        <v>122291599</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403599</v>
+        <v>403740</v>
       </c>
       <c r="R20" t="n">
-        <v>7064658</v>
+        <v>7064407</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2784,7 +2784,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291594</v>
+        <v>122291588</v>
       </c>
       <c r="B21" t="n">
         <v>57374</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>404077</v>
+        <v>403772</v>
       </c>
       <c r="R21" t="n">
-        <v>7064478</v>
+        <v>7064456</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,7 +2891,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291595</v>
+        <v>122291592</v>
       </c>
       <c r="B22" t="n">
         <v>57374</v>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>403755</v>
+        <v>403956</v>
       </c>
       <c r="R22" t="n">
-        <v>7064690</v>
+        <v>7064405</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291594</v>
+        <v>122291588</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404077</v>
+        <v>403772</v>
       </c>
       <c r="R8" t="n">
-        <v>7064478</v>
+        <v>7064456</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291598</v>
+        <v>122291591</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403536</v>
+        <v>403825</v>
       </c>
       <c r="R9" t="n">
-        <v>7064668</v>
+        <v>7064511</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291595</v>
+        <v>122291614</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403755</v>
+        <v>403721</v>
       </c>
       <c r="R10" t="n">
-        <v>7064690</v>
+        <v>7064419</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291597</v>
+        <v>122291613</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403599</v>
+        <v>403571</v>
       </c>
       <c r="R11" t="n">
-        <v>7064658</v>
+        <v>7064657</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291596</v>
+        <v>122291599</v>
       </c>
       <c r="B12" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403524</v>
+        <v>403740</v>
       </c>
       <c r="R12" t="n">
-        <v>7065024</v>
+        <v>7064407</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291593</v>
+        <v>122291595</v>
       </c>
       <c r="B13" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404072</v>
+        <v>403755</v>
       </c>
       <c r="R13" t="n">
-        <v>7064465</v>
+        <v>7064690</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291611</v>
+        <v>122291593</v>
       </c>
       <c r="B14" t="n">
-        <v>57321</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,20 +2035,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102620</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2056,29 +2056,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403666</v>
+        <v>404072</v>
       </c>
       <c r="R14" t="n">
-        <v>7064579</v>
+        <v>7064465</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291613</v>
+        <v>122291590</v>
       </c>
       <c r="B15" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403571</v>
+        <v>403811</v>
       </c>
       <c r="R15" t="n">
-        <v>7064657</v>
+        <v>7064538</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2210,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291589</v>
+        <v>122291594</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403803</v>
+        <v>404077</v>
       </c>
       <c r="R16" t="n">
-        <v>7064528</v>
+        <v>7064478</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2317,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291591</v>
+        <v>122291589</v>
       </c>
       <c r="B17" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403825</v>
+        <v>403803</v>
       </c>
       <c r="R17" t="n">
-        <v>7064511</v>
+        <v>7064528</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291590</v>
+        <v>122291596</v>
       </c>
       <c r="B18" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,10 +2491,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403811</v>
+        <v>403524</v>
       </c>
       <c r="R18" t="n">
-        <v>7064538</v>
+        <v>7065024</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2543,7 +2531,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2570,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291614</v>
+        <v>122291597</v>
       </c>
       <c r="B19" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,21 +2574,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2610,10 +2598,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403721</v>
+        <v>403599</v>
       </c>
       <c r="R19" t="n">
-        <v>7064419</v>
+        <v>7064658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2650,7 +2638,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291599</v>
+        <v>122291592</v>
       </c>
       <c r="B20" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2717,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403740</v>
+        <v>403956</v>
       </c>
       <c r="R20" t="n">
-        <v>7064407</v>
+        <v>7064405</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2757,7 +2745,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2784,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291588</v>
+        <v>122291598</v>
       </c>
       <c r="B21" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2824,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403772</v>
+        <v>403536</v>
       </c>
       <c r="R21" t="n">
-        <v>7064456</v>
+        <v>7064668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2864,7 +2852,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,10 +2879,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291592</v>
+        <v>122291611</v>
       </c>
       <c r="B22" t="n">
-        <v>57374</v>
+        <v>57326</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2903,20 +2891,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>102620</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2924,17 +2912,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>403956</v>
+        <v>403666</v>
       </c>
       <c r="R22" t="n">
-        <v>7064405</v>
+        <v>7064579</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291588</v>
+        <v>122291614</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,21 +1397,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403772</v>
+        <v>403721</v>
       </c>
       <c r="R8" t="n">
-        <v>7064456</v>
+        <v>7064419</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291614</v>
+        <v>122291598</v>
       </c>
       <c r="B10" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403721</v>
+        <v>403536</v>
       </c>
       <c r="R10" t="n">
-        <v>7064419</v>
+        <v>7064668</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291613</v>
+        <v>122291593</v>
       </c>
       <c r="B11" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403571</v>
+        <v>404072</v>
       </c>
       <c r="R11" t="n">
-        <v>7064657</v>
+        <v>7064465</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,7 +1809,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291599</v>
+        <v>122291590</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403740</v>
+        <v>403811</v>
       </c>
       <c r="R12" t="n">
-        <v>7064407</v>
+        <v>7064538</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,7 +1916,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291595</v>
+        <v>122291588</v>
       </c>
       <c r="B13" t="n">
         <v>57379</v>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403755</v>
+        <v>403772</v>
       </c>
       <c r="R13" t="n">
-        <v>7064690</v>
+        <v>7064456</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291593</v>
+        <v>122291589</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404072</v>
+        <v>403803</v>
       </c>
       <c r="R14" t="n">
-        <v>7064465</v>
+        <v>7064528</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291590</v>
+        <v>122291594</v>
       </c>
       <c r="B15" t="n">
         <v>57379</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403811</v>
+        <v>404077</v>
       </c>
       <c r="R15" t="n">
-        <v>7064538</v>
+        <v>7064478</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291594</v>
+        <v>122291599</v>
       </c>
       <c r="B16" t="n">
         <v>57379</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404077</v>
+        <v>403740</v>
       </c>
       <c r="R16" t="n">
-        <v>7064478</v>
+        <v>7064407</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291589</v>
+        <v>122291613</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2360,21 +2360,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403803</v>
+        <v>403571</v>
       </c>
       <c r="R17" t="n">
-        <v>7064528</v>
+        <v>7064657</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2665,7 +2665,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291592</v>
+        <v>122291595</v>
       </c>
       <c r="B20" t="n">
         <v>57379</v>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403956</v>
+        <v>403755</v>
       </c>
       <c r="R20" t="n">
-        <v>7064405</v>
+        <v>7064690</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291598</v>
+        <v>122291611</v>
       </c>
       <c r="B21" t="n">
-        <v>57379</v>
+        <v>57326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2784,20 +2784,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>102620</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2805,17 +2805,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403536</v>
+        <v>403666</v>
       </c>
       <c r="R21" t="n">
-        <v>7064668</v>
+        <v>7064579</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2852,7 +2864,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2879,10 +2891,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291611</v>
+        <v>122291592</v>
       </c>
       <c r="B22" t="n">
-        <v>57326</v>
+        <v>57379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2891,20 +2903,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102620</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2912,29 +2924,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>403666</v>
+        <v>403956</v>
       </c>
       <c r="R22" t="n">
-        <v>7064579</v>
+        <v>7064405</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -2344,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291613</v>
+        <v>122291596</v>
       </c>
       <c r="B17" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2360,21 +2360,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403571</v>
+        <v>403524</v>
       </c>
       <c r="R17" t="n">
-        <v>7064657</v>
+        <v>7065024</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291596</v>
+        <v>122291597</v>
       </c>
       <c r="B18" t="n">
         <v>57379</v>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403524</v>
+        <v>403599</v>
       </c>
       <c r="R18" t="n">
-        <v>7065024</v>
+        <v>7064658</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,7 +2558,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291597</v>
+        <v>122291595</v>
       </c>
       <c r="B19" t="n">
         <v>57379</v>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403599</v>
+        <v>403755</v>
       </c>
       <c r="R19" t="n">
-        <v>7064658</v>
+        <v>7064690</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291595</v>
+        <v>122291613</v>
       </c>
       <c r="B20" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,21 +2681,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403755</v>
+        <v>403571</v>
       </c>
       <c r="R20" t="n">
-        <v>7064690</v>
+        <v>7064657</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291614</v>
+        <v>122291611</v>
       </c>
       <c r="B8" t="n">
-        <v>78651</v>
+        <v>57326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,38 +1393,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>102620</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403721</v>
+        <v>403666</v>
       </c>
       <c r="R8" t="n">
-        <v>7064419</v>
+        <v>7064579</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1468,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,7 +1495,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291591</v>
+        <v>122291592</v>
       </c>
       <c r="B9" t="n">
         <v>57379</v>
@@ -1506,11 +1513,6 @@
       <c r="E9" t="n">
         <v>100109</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1528,10 +1530,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403825</v>
+        <v>403956</v>
       </c>
       <c r="R9" t="n">
-        <v>7064511</v>
+        <v>7064405</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,7 +1597,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291598</v>
+        <v>122291590</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1613,11 +1615,6 @@
       <c r="E10" t="n">
         <v>100109</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1635,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403536</v>
+        <v>403811</v>
       </c>
       <c r="R10" t="n">
-        <v>7064668</v>
+        <v>7064538</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1672,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,7 +1699,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291593</v>
+        <v>122291598</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1720,11 +1717,6 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1742,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404072</v>
+        <v>403536</v>
       </c>
       <c r="R11" t="n">
-        <v>7064465</v>
+        <v>7064668</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1774,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,7 +1801,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291590</v>
+        <v>122291594</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1827,11 +1819,6 @@
       <c r="E12" t="n">
         <v>100109</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1849,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403811</v>
+        <v>404077</v>
       </c>
       <c r="R12" t="n">
-        <v>7064538</v>
+        <v>7064478</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1876,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,7 +1903,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291588</v>
+        <v>122291595</v>
       </c>
       <c r="B13" t="n">
         <v>57379</v>
@@ -1934,11 +1921,6 @@
       <c r="E13" t="n">
         <v>100109</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1956,10 +1938,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403772</v>
+        <v>403755</v>
       </c>
       <c r="R13" t="n">
-        <v>7064456</v>
+        <v>7064690</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2005,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291589</v>
+        <v>122291591</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -2041,11 +2023,6 @@
       <c r="E14" t="n">
         <v>100109</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2063,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403803</v>
+        <v>403825</v>
       </c>
       <c r="R14" t="n">
-        <v>7064528</v>
+        <v>7064511</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2107,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291594</v>
+        <v>122291593</v>
       </c>
       <c r="B15" t="n">
         <v>57379</v>
@@ -2148,11 +2125,6 @@
       <c r="E15" t="n">
         <v>100109</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2170,10 +2142,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404077</v>
+        <v>404072</v>
       </c>
       <c r="R15" t="n">
-        <v>7064478</v>
+        <v>7064465</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2182,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,7 +2209,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291599</v>
+        <v>122291596</v>
       </c>
       <c r="B16" t="n">
         <v>57379</v>
@@ -2255,11 +2227,6 @@
       <c r="E16" t="n">
         <v>100109</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2277,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403740</v>
+        <v>403524</v>
       </c>
       <c r="R16" t="n">
-        <v>7064407</v>
+        <v>7065024</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2284,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,7 +2311,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291596</v>
+        <v>122291599</v>
       </c>
       <c r="B17" t="n">
         <v>57379</v>
@@ -2362,11 +2329,6 @@
       <c r="E17" t="n">
         <v>100109</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2384,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403524</v>
+        <v>403740</v>
       </c>
       <c r="R17" t="n">
-        <v>7065024</v>
+        <v>7064407</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2424,7 +2386,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,10 +2413,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291597</v>
+        <v>122291613</v>
       </c>
       <c r="B18" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,21 +2429,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2491,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403599</v>
+        <v>403571</v>
       </c>
       <c r="R18" t="n">
-        <v>7064658</v>
+        <v>7064657</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,7 +2488,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,7 +2515,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291595</v>
+        <v>122291588</v>
       </c>
       <c r="B19" t="n">
         <v>57379</v>
@@ -2576,11 +2533,6 @@
       <c r="E19" t="n">
         <v>100109</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2598,10 +2550,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403755</v>
+        <v>403772</v>
       </c>
       <c r="R19" t="n">
-        <v>7064690</v>
+        <v>7064456</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2665,10 +2617,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291613</v>
+        <v>122291597</v>
       </c>
       <c r="B20" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,21 +2633,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2705,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403571</v>
+        <v>403599</v>
       </c>
       <c r="R20" t="n">
-        <v>7064657</v>
+        <v>7064658</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,7 +2692,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2772,10 +2719,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291611</v>
+        <v>122291614</v>
       </c>
       <c r="B21" t="n">
-        <v>57326</v>
+        <v>78652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2784,50 +2731,33 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102620</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Hökuggla</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403666</v>
+        <v>403721</v>
       </c>
       <c r="R21" t="n">
-        <v>7064579</v>
+        <v>7064419</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2864,7 +2794,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,7 +2821,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291592</v>
+        <v>122291589</v>
       </c>
       <c r="B22" t="n">
         <v>57379</v>
@@ -2909,11 +2839,6 @@
       <c r="E22" t="n">
         <v>100109</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2931,10 +2856,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>403956</v>
+        <v>403803</v>
       </c>
       <c r="R22" t="n">
-        <v>7064405</v>
+        <v>7064528</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291611</v>
+        <v>122291594</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,15 +1393,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102620</v>
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1409,29 +1414,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403666</v>
+        <v>404077</v>
       </c>
       <c r="R8" t="n">
-        <v>7064579</v>
+        <v>7064478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291592</v>
+        <v>122291614</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,16 +1504,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1530,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403956</v>
+        <v>403721</v>
       </c>
       <c r="R9" t="n">
-        <v>7064405</v>
+        <v>7064419</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1568,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291590</v>
+        <v>122291596</v>
       </c>
       <c r="B10" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,6 +1613,11 @@
       <c r="E10" t="n">
         <v>100109</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1632,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403811</v>
+        <v>403524</v>
       </c>
       <c r="R10" t="n">
-        <v>7064538</v>
+        <v>7065024</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1675,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291598</v>
+        <v>122291589</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,6 +1720,11 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1734,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403536</v>
+        <v>403803</v>
       </c>
       <c r="R11" t="n">
-        <v>7064668</v>
+        <v>7064528</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1774,7 +1782,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291594</v>
+        <v>122291592</v>
       </c>
       <c r="B12" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,6 +1827,11 @@
       <c r="E12" t="n">
         <v>100109</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1836,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404077</v>
+        <v>403956</v>
       </c>
       <c r="R12" t="n">
-        <v>7064478</v>
+        <v>7064405</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,7 +1889,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291595</v>
+        <v>122291613</v>
       </c>
       <c r="B13" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,16 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1938,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403755</v>
+        <v>403571</v>
       </c>
       <c r="R13" t="n">
-        <v>7064690</v>
+        <v>7064657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1996,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291591</v>
+        <v>122291599</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,6 +2041,11 @@
       <c r="E14" t="n">
         <v>100109</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2040,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403825</v>
+        <v>403740</v>
       </c>
       <c r="R14" t="n">
-        <v>7064511</v>
+        <v>7064407</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291593</v>
+        <v>122291591</v>
       </c>
       <c r="B15" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2125,6 +2148,11 @@
       <c r="E15" t="n">
         <v>100109</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2142,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404072</v>
+        <v>403825</v>
       </c>
       <c r="R15" t="n">
-        <v>7064465</v>
+        <v>7064511</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291596</v>
+        <v>122291588</v>
       </c>
       <c r="B16" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2227,6 +2255,11 @@
       <c r="E16" t="n">
         <v>100109</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2244,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403524</v>
+        <v>403772</v>
       </c>
       <c r="R16" t="n">
-        <v>7065024</v>
+        <v>7064456</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,7 +2317,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2311,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291599</v>
+        <v>122291590</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2329,6 +2362,11 @@
       <c r="E17" t="n">
         <v>100109</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2346,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403740</v>
+        <v>403811</v>
       </c>
       <c r="R17" t="n">
-        <v>7064407</v>
+        <v>7064538</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,7 +2424,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2413,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291613</v>
+        <v>122291593</v>
       </c>
       <c r="B18" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2429,16 +2467,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2448,10 +2491,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403571</v>
+        <v>404072</v>
       </c>
       <c r="R18" t="n">
-        <v>7064657</v>
+        <v>7064465</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,7 +2531,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2515,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291588</v>
+        <v>122291595</v>
       </c>
       <c r="B19" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2533,6 +2576,11 @@
       <c r="E19" t="n">
         <v>100109</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2550,10 +2598,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403772</v>
+        <v>403755</v>
       </c>
       <c r="R19" t="n">
-        <v>7064456</v>
+        <v>7064690</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2617,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291597</v>
+        <v>122291611</v>
       </c>
       <c r="B20" t="n">
-        <v>57379</v>
+        <v>57330</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2629,15 +2677,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>102620</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2645,17 +2698,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403599</v>
+        <v>403666</v>
       </c>
       <c r="R20" t="n">
-        <v>7064658</v>
+        <v>7064579</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,7 +2757,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2719,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291614</v>
+        <v>122291597</v>
       </c>
       <c r="B21" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2735,16 +2800,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2824,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403721</v>
+        <v>403599</v>
       </c>
       <c r="R21" t="n">
-        <v>7064419</v>
+        <v>7064658</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2794,7 +2864,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2821,10 +2891,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291589</v>
+        <v>122291598</v>
       </c>
       <c r="B22" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2839,6 +2909,11 @@
       <c r="E22" t="n">
         <v>100109</v>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2856,10 +2931,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>403803</v>
+        <v>403536</v>
       </c>
       <c r="R22" t="n">
-        <v>7064528</v>
+        <v>7064668</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2896,7 +2971,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291594</v>
+        <v>122291597</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404077</v>
+        <v>403599</v>
       </c>
       <c r="R8" t="n">
-        <v>7064478</v>
+        <v>7064658</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291614</v>
+        <v>122291613</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403721</v>
+        <v>403571</v>
       </c>
       <c r="R9" t="n">
-        <v>7064419</v>
+        <v>7064657</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291596</v>
+        <v>122291592</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403524</v>
+        <v>403956</v>
       </c>
       <c r="R10" t="n">
-        <v>7065024</v>
+        <v>7064405</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291589</v>
+        <v>122291596</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403803</v>
+        <v>403524</v>
       </c>
       <c r="R11" t="n">
-        <v>7064528</v>
+        <v>7065024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,7 +1809,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291592</v>
+        <v>122291594</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403956</v>
+        <v>404077</v>
       </c>
       <c r="R12" t="n">
-        <v>7064405</v>
+        <v>7064478</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,7 +1916,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291613</v>
+        <v>122291614</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403571</v>
+        <v>403721</v>
       </c>
       <c r="R13" t="n">
-        <v>7064657</v>
+        <v>7064419</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291599</v>
+        <v>122291588</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403740</v>
+        <v>403772</v>
       </c>
       <c r="R14" t="n">
-        <v>7064407</v>
+        <v>7064456</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,7 +2130,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291591</v>
+        <v>122291599</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403825</v>
+        <v>403740</v>
       </c>
       <c r="R15" t="n">
-        <v>7064511</v>
+        <v>7064407</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291588</v>
+        <v>122291595</v>
       </c>
       <c r="B16" t="n">
         <v>57383</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403772</v>
+        <v>403755</v>
       </c>
       <c r="R16" t="n">
-        <v>7064456</v>
+        <v>7064690</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291590</v>
+        <v>122291591</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403811</v>
+        <v>403825</v>
       </c>
       <c r="R17" t="n">
-        <v>7064538</v>
+        <v>7064511</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291593</v>
+        <v>122291590</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>404072</v>
+        <v>403811</v>
       </c>
       <c r="R18" t="n">
-        <v>7064465</v>
+        <v>7064538</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291595</v>
+        <v>122291598</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403755</v>
+        <v>403536</v>
       </c>
       <c r="R19" t="n">
-        <v>7064690</v>
+        <v>7064668</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291611</v>
+        <v>122291593</v>
       </c>
       <c r="B20" t="n">
-        <v>57330</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2677,20 +2677,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102620</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2698,29 +2698,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403666</v>
+        <v>404072</v>
       </c>
       <c r="R20" t="n">
-        <v>7064579</v>
+        <v>7064465</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2757,7 +2745,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2784,7 +2772,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291597</v>
+        <v>122291589</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2824,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403599</v>
+        <v>403803</v>
       </c>
       <c r="R21" t="n">
-        <v>7064658</v>
+        <v>7064528</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2891,32 +2879,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291598</v>
+        <v>122291611</v>
       </c>
       <c r="B22" t="n">
-        <v>57383</v>
+        <v>57330</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>102620</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2924,17 +2912,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nötnäsdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>403536</v>
+        <v>403666</v>
       </c>
       <c r="R22" t="n">
-        <v>7064668</v>
+        <v>7064579</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>Hörde först obekanta läten, sedan fick jag syn på den då den satte sig i en grantopp och spanade ett tag.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291597</v>
+        <v>122291598</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403599</v>
+        <v>403536</v>
       </c>
       <c r="R8" t="n">
-        <v>7064658</v>
+        <v>7064668</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291613</v>
+        <v>122291594</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,21 +1504,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403571</v>
+        <v>404077</v>
       </c>
       <c r="R9" t="n">
-        <v>7064657</v>
+        <v>7064478</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291592</v>
+        <v>122291596</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403956</v>
+        <v>403524</v>
       </c>
       <c r="R10" t="n">
-        <v>7064405</v>
+        <v>7065024</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291596</v>
+        <v>122291593</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403524</v>
+        <v>404072</v>
       </c>
       <c r="R11" t="n">
-        <v>7065024</v>
+        <v>7064465</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,7 +1809,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291594</v>
+        <v>122291595</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404077</v>
+        <v>403755</v>
       </c>
       <c r="R12" t="n">
-        <v>7064478</v>
+        <v>7064690</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,7 +1916,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291614</v>
+        <v>122291613</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403721</v>
+        <v>403571</v>
       </c>
       <c r="R13" t="n">
-        <v>7064419</v>
+        <v>7064657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291588</v>
+        <v>122291599</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403772</v>
+        <v>403740</v>
       </c>
       <c r="R14" t="n">
-        <v>7064456</v>
+        <v>7064407</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291599</v>
+        <v>122291614</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403740</v>
+        <v>403721</v>
       </c>
       <c r="R15" t="n">
-        <v>7064407</v>
+        <v>7064419</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291595</v>
+        <v>122291592</v>
       </c>
       <c r="B16" t="n">
         <v>57383</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403755</v>
+        <v>403956</v>
       </c>
       <c r="R16" t="n">
-        <v>7064690</v>
+        <v>7064405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291591</v>
+        <v>122291597</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403825</v>
+        <v>403599</v>
       </c>
       <c r="R17" t="n">
-        <v>7064511</v>
+        <v>7064658</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291590</v>
+        <v>122291589</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403811</v>
+        <v>403803</v>
       </c>
       <c r="R18" t="n">
-        <v>7064538</v>
+        <v>7064528</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291598</v>
+        <v>122291590</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403536</v>
+        <v>403811</v>
       </c>
       <c r="R19" t="n">
-        <v>7064668</v>
+        <v>7064538</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,7 +2665,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291593</v>
+        <v>122291591</v>
       </c>
       <c r="B20" t="n">
         <v>57383</v>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>404072</v>
+        <v>403825</v>
       </c>
       <c r="R20" t="n">
-        <v>7064465</v>
+        <v>7064511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,7 +2772,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291589</v>
+        <v>122291588</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403803</v>
+        <v>403772</v>
       </c>
       <c r="R21" t="n">
-        <v>7064528</v>
+        <v>7064456</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291613</v>
+        <v>122291599</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403571</v>
+        <v>403740</v>
       </c>
       <c r="R13" t="n">
-        <v>7064657</v>
+        <v>7064407</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291599</v>
+        <v>122291613</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403740</v>
+        <v>403571</v>
       </c>
       <c r="R14" t="n">
-        <v>7064407</v>
+        <v>7064657</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291598</v>
+        <v>122291591</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403536</v>
+        <v>403825</v>
       </c>
       <c r="R8" t="n">
-        <v>7064668</v>
+        <v>7064511</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291594</v>
+        <v>122291596</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404077</v>
+        <v>403524</v>
       </c>
       <c r="R9" t="n">
-        <v>7064478</v>
+        <v>7065024</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291596</v>
+        <v>122291593</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403524</v>
+        <v>404072</v>
       </c>
       <c r="R10" t="n">
-        <v>7065024</v>
+        <v>7064465</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291593</v>
+        <v>122291597</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404072</v>
+        <v>403599</v>
       </c>
       <c r="R11" t="n">
-        <v>7064465</v>
+        <v>7064658</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1809,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291595</v>
+        <v>122291589</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403755</v>
+        <v>403803</v>
       </c>
       <c r="R12" t="n">
-        <v>7064690</v>
+        <v>7064528</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2023,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291613</v>
+        <v>122291592</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403571</v>
+        <v>403956</v>
       </c>
       <c r="R14" t="n">
-        <v>7064657</v>
+        <v>7064405</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291614</v>
+        <v>122291595</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403721</v>
+        <v>403755</v>
       </c>
       <c r="R15" t="n">
-        <v>7064419</v>
+        <v>7064690</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291592</v>
+        <v>122291613</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403956</v>
+        <v>403571</v>
       </c>
       <c r="R16" t="n">
-        <v>7064405</v>
+        <v>7064657</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,7 +2344,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291597</v>
+        <v>122291590</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403599</v>
+        <v>403811</v>
       </c>
       <c r="R17" t="n">
-        <v>7064658</v>
+        <v>7064538</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291589</v>
+        <v>122291614</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,21 +2467,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403803</v>
+        <v>403721</v>
       </c>
       <c r="R18" t="n">
-        <v>7064528</v>
+        <v>7064419</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,7 +2558,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291590</v>
+        <v>122291594</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403811</v>
+        <v>404077</v>
       </c>
       <c r="R19" t="n">
-        <v>7064538</v>
+        <v>7064478</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,7 +2665,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291591</v>
+        <v>122291588</v>
       </c>
       <c r="B20" t="n">
         <v>57383</v>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403825</v>
+        <v>403772</v>
       </c>
       <c r="R20" t="n">
-        <v>7064511</v>
+        <v>7064456</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,7 +2772,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291588</v>
+        <v>122291598</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403772</v>
+        <v>403536</v>
       </c>
       <c r="R21" t="n">
-        <v>7064456</v>
+        <v>7064668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291591</v>
+        <v>122291597</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403825</v>
+        <v>403599</v>
       </c>
       <c r="R8" t="n">
-        <v>7064511</v>
+        <v>7064658</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291596</v>
+        <v>122291589</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403524</v>
+        <v>403803</v>
       </c>
       <c r="R9" t="n">
-        <v>7065024</v>
+        <v>7064528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291593</v>
+        <v>122291596</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404072</v>
+        <v>403524</v>
       </c>
       <c r="R10" t="n">
-        <v>7064465</v>
+        <v>7065024</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291597</v>
+        <v>122291592</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403599</v>
+        <v>403956</v>
       </c>
       <c r="R11" t="n">
-        <v>7064658</v>
+        <v>7064405</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291589</v>
+        <v>122291614</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,21 +1825,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403803</v>
+        <v>403721</v>
       </c>
       <c r="R12" t="n">
-        <v>7064528</v>
+        <v>7064419</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,7 +1916,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291599</v>
+        <v>122291594</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403740</v>
+        <v>404077</v>
       </c>
       <c r="R13" t="n">
-        <v>7064407</v>
+        <v>7064478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291592</v>
+        <v>122291599</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403956</v>
+        <v>403740</v>
       </c>
       <c r="R14" t="n">
-        <v>7064405</v>
+        <v>7064407</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,7 +2130,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291595</v>
+        <v>122291591</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403755</v>
+        <v>403825</v>
       </c>
       <c r="R15" t="n">
-        <v>7064690</v>
+        <v>7064511</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291613</v>
+        <v>122291598</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403571</v>
+        <v>403536</v>
       </c>
       <c r="R16" t="n">
-        <v>7064657</v>
+        <v>7064668</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,7 +2344,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291590</v>
+        <v>122291588</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403811</v>
+        <v>403772</v>
       </c>
       <c r="R17" t="n">
-        <v>7064538</v>
+        <v>7064456</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291614</v>
+        <v>122291593</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,21 +2467,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403721</v>
+        <v>404072</v>
       </c>
       <c r="R18" t="n">
-        <v>7064419</v>
+        <v>7064465</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291594</v>
+        <v>122291613</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2574,21 +2574,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>404077</v>
+        <v>403571</v>
       </c>
       <c r="R19" t="n">
-        <v>7064478</v>
+        <v>7064657</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,7 +2665,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291588</v>
+        <v>122291590</v>
       </c>
       <c r="B20" t="n">
         <v>57383</v>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403772</v>
+        <v>403811</v>
       </c>
       <c r="R20" t="n">
-        <v>7064456</v>
+        <v>7064538</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,7 +2772,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291598</v>
+        <v>122291595</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403536</v>
+        <v>403755</v>
       </c>
       <c r="R21" t="n">
-        <v>7064668</v>
+        <v>7064690</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291597</v>
+        <v>122291594</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403599</v>
+        <v>404077</v>
       </c>
       <c r="R8" t="n">
-        <v>7064658</v>
+        <v>7064478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291589</v>
+        <v>122291599</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403803</v>
+        <v>403740</v>
       </c>
       <c r="R9" t="n">
-        <v>7064528</v>
+        <v>7064407</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291596</v>
+        <v>122291589</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403524</v>
+        <v>403803</v>
       </c>
       <c r="R10" t="n">
-        <v>7065024</v>
+        <v>7064528</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291592</v>
+        <v>122291591</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403956</v>
+        <v>403825</v>
       </c>
       <c r="R11" t="n">
-        <v>7064405</v>
+        <v>7064511</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291614</v>
+        <v>122291590</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,21 +1825,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403721</v>
+        <v>403811</v>
       </c>
       <c r="R12" t="n">
-        <v>7064419</v>
+        <v>7064538</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291594</v>
+        <v>122291588</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404077</v>
+        <v>403772</v>
       </c>
       <c r="R13" t="n">
-        <v>7064478</v>
+        <v>7064456</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291599</v>
+        <v>122291597</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403740</v>
+        <v>403599</v>
       </c>
       <c r="R14" t="n">
-        <v>7064407</v>
+        <v>7064658</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291591</v>
+        <v>122291613</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403825</v>
+        <v>403571</v>
       </c>
       <c r="R15" t="n">
-        <v>7064511</v>
+        <v>7064657</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291598</v>
+        <v>122291593</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403536</v>
+        <v>404072</v>
       </c>
       <c r="R16" t="n">
-        <v>7064668</v>
+        <v>7064465</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291588</v>
+        <v>122291596</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403772</v>
+        <v>403524</v>
       </c>
       <c r="R17" t="n">
-        <v>7064456</v>
+        <v>7065024</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291593</v>
+        <v>122291598</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>404072</v>
+        <v>403536</v>
       </c>
       <c r="R18" t="n">
-        <v>7064465</v>
+        <v>7064668</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291613</v>
+        <v>122291595</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2574,21 +2574,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403571</v>
+        <v>403755</v>
       </c>
       <c r="R19" t="n">
-        <v>7064657</v>
+        <v>7064690</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291590</v>
+        <v>122291614</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,21 +2681,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403811</v>
+        <v>403721</v>
       </c>
       <c r="R20" t="n">
-        <v>7064538</v>
+        <v>7064419</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291595</v>
+        <v>122291592</v>
       </c>
       <c r="B21" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403755</v>
+        <v>403956</v>
       </c>
       <c r="R21" t="n">
-        <v>7064690</v>
+        <v>7064405</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2882,7 +2882,7 @@
         <v>122291611</v>
       </c>
       <c r="B22" t="n">
-        <v>57330</v>
+        <v>57331</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291594</v>
+        <v>122291592</v>
       </c>
       <c r="B8" t="n">
         <v>57384</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404077</v>
+        <v>403956</v>
       </c>
       <c r="R8" t="n">
-        <v>7064478</v>
+        <v>7064405</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291599</v>
+        <v>122291588</v>
       </c>
       <c r="B9" t="n">
         <v>57384</v>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403740</v>
+        <v>403772</v>
       </c>
       <c r="R9" t="n">
-        <v>7064407</v>
+        <v>7064456</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291589</v>
+        <v>122291599</v>
       </c>
       <c r="B10" t="n">
         <v>57384</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403803</v>
+        <v>403740</v>
       </c>
       <c r="R10" t="n">
-        <v>7064528</v>
+        <v>7064407</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291591</v>
+        <v>122291590</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403825</v>
+        <v>403811</v>
       </c>
       <c r="R11" t="n">
-        <v>7064511</v>
+        <v>7064538</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1809,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291590</v>
+        <v>122291589</v>
       </c>
       <c r="B12" t="n">
         <v>57384</v>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403811</v>
+        <v>403803</v>
       </c>
       <c r="R12" t="n">
-        <v>7064538</v>
+        <v>7064528</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291588</v>
+        <v>122291591</v>
       </c>
       <c r="B13" t="n">
         <v>57384</v>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403772</v>
+        <v>403825</v>
       </c>
       <c r="R13" t="n">
-        <v>7064456</v>
+        <v>7064511</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291597</v>
+        <v>122291593</v>
       </c>
       <c r="B14" t="n">
         <v>57384</v>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403599</v>
+        <v>404072</v>
       </c>
       <c r="R14" t="n">
-        <v>7064658</v>
+        <v>7064465</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291613</v>
+        <v>122291598</v>
       </c>
       <c r="B15" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403571</v>
+        <v>403536</v>
       </c>
       <c r="R15" t="n">
-        <v>7064657</v>
+        <v>7064668</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291593</v>
+        <v>122291594</v>
       </c>
       <c r="B16" t="n">
         <v>57384</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404072</v>
+        <v>404077</v>
       </c>
       <c r="R16" t="n">
-        <v>7064465</v>
+        <v>7064478</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291596</v>
+        <v>122291613</v>
       </c>
       <c r="B17" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2360,21 +2360,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403524</v>
+        <v>403571</v>
       </c>
       <c r="R17" t="n">
-        <v>7065024</v>
+        <v>7064657</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291598</v>
+        <v>122291614</v>
       </c>
       <c r="B18" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,21 +2467,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403536</v>
+        <v>403721</v>
       </c>
       <c r="R18" t="n">
-        <v>7064668</v>
+        <v>7064419</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,7 +2558,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291595</v>
+        <v>122291596</v>
       </c>
       <c r="B19" t="n">
         <v>57384</v>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403755</v>
+        <v>403524</v>
       </c>
       <c r="R19" t="n">
-        <v>7064690</v>
+        <v>7065024</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291614</v>
+        <v>122291597</v>
       </c>
       <c r="B20" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,21 +2681,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403721</v>
+        <v>403599</v>
       </c>
       <c r="R20" t="n">
-        <v>7064419</v>
+        <v>7064658</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2772,7 +2772,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291592</v>
+        <v>122291595</v>
       </c>
       <c r="B21" t="n">
         <v>57384</v>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403956</v>
+        <v>403755</v>
       </c>
       <c r="R21" t="n">
-        <v>7064405</v>
+        <v>7064690</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291592</v>
+        <v>122291599</v>
       </c>
       <c r="B8" t="n">
         <v>57384</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403956</v>
+        <v>403740</v>
       </c>
       <c r="R8" t="n">
-        <v>7064405</v>
+        <v>7064407</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291588</v>
+        <v>122291589</v>
       </c>
       <c r="B9" t="n">
         <v>57384</v>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403772</v>
+        <v>403803</v>
       </c>
       <c r="R9" t="n">
-        <v>7064456</v>
+        <v>7064528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291599</v>
+        <v>122291592</v>
       </c>
       <c r="B10" t="n">
         <v>57384</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403740</v>
+        <v>403956</v>
       </c>
       <c r="R10" t="n">
-        <v>7064407</v>
+        <v>7064405</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291590</v>
+        <v>122291594</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403811</v>
+        <v>404077</v>
       </c>
       <c r="R11" t="n">
-        <v>7064538</v>
+        <v>7064478</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,7 +1809,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291589</v>
+        <v>122291596</v>
       </c>
       <c r="B12" t="n">
         <v>57384</v>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403803</v>
+        <v>403524</v>
       </c>
       <c r="R12" t="n">
-        <v>7064528</v>
+        <v>7065024</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,7 +1916,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291591</v>
+        <v>122291593</v>
       </c>
       <c r="B13" t="n">
         <v>57384</v>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403825</v>
+        <v>404072</v>
       </c>
       <c r="R13" t="n">
-        <v>7064511</v>
+        <v>7064465</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291593</v>
+        <v>122291591</v>
       </c>
       <c r="B14" t="n">
         <v>57384</v>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404072</v>
+        <v>403825</v>
       </c>
       <c r="R14" t="n">
-        <v>7064465</v>
+        <v>7064511</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291598</v>
+        <v>122291613</v>
       </c>
       <c r="B15" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403536</v>
+        <v>403571</v>
       </c>
       <c r="R15" t="n">
-        <v>7064668</v>
+        <v>7064657</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291594</v>
+        <v>122291597</v>
       </c>
       <c r="B16" t="n">
         <v>57384</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404077</v>
+        <v>403599</v>
       </c>
       <c r="R16" t="n">
-        <v>7064478</v>
+        <v>7064658</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291613</v>
+        <v>122291588</v>
       </c>
       <c r="B17" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2360,21 +2360,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403571</v>
+        <v>403772</v>
       </c>
       <c r="R17" t="n">
-        <v>7064657</v>
+        <v>7064456</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291614</v>
+        <v>122291590</v>
       </c>
       <c r="B18" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,21 +2467,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403721</v>
+        <v>403811</v>
       </c>
       <c r="R18" t="n">
-        <v>7064419</v>
+        <v>7064538</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,7 +2558,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291596</v>
+        <v>122291595</v>
       </c>
       <c r="B19" t="n">
         <v>57384</v>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403524</v>
+        <v>403755</v>
       </c>
       <c r="R19" t="n">
-        <v>7065024</v>
+        <v>7064690</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291597</v>
+        <v>122291614</v>
       </c>
       <c r="B20" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,21 +2681,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403599</v>
+        <v>403721</v>
       </c>
       <c r="R20" t="n">
-        <v>7064658</v>
+        <v>7064419</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2772,7 +2772,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291595</v>
+        <v>122291598</v>
       </c>
       <c r="B21" t="n">
         <v>57384</v>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403755</v>
+        <v>403536</v>
       </c>
       <c r="R21" t="n">
-        <v>7064690</v>
+        <v>7064668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55393-2024 artfynd.xlsx
+++ b/artfynd/A 55393-2024 artfynd.xlsx
@@ -2882,7 +2882,7 @@
         <v>122291611</v>
       </c>
       <c r="B22" t="n">
-        <v>57331</v>
+        <v>57425</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
